--- a/apps/api/data/db/CRM_CONTACTOS_v1.xlsx
+++ b/apps/api/data/db/CRM_CONTACTOS_v1.xlsx
@@ -603,7 +603,7 @@
       <c r="H9" s="4" t="n"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Las dos fechas son opcionales; formato AAAA-MM-DD.</t>
+          <t>Fechas opcionales: AAAA-MM-DD o DD/MM/AAAA; 'Sin Pagos' equivale a sin vencimiento.</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       <c r="H10" s="4" t="n"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DNI y Teléfono deben conservarse como texto.</t>
+          <t>DNI y Teléfono como texto. Con ARS: 10 dígitos locales o +54 9 y 10 dígitos.</t>
         </is>
       </c>
     </row>
